--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92565645266</v>
+        <v>46157.93089437143</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93089437143</v>
+        <v>46157.93167394023</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93167394023</v>
+        <v>46157.9339762655</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9339762655</v>
+        <v>46157.93715340181</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93715340181</v>
+        <v>46158.28214028107</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214028107</v>
+        <v>46158.29675372668</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29675372668</v>
+        <v>46158.2981204313</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2981204313</v>
+        <v>46158.33384892391</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33384892391</v>
+        <v>46158.36854351987</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/33. СЕВЭНКО (ХВС и водоотведение) Энтузиастов, 75/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36854351987</v>
+        <v>46158.37285088252</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
